--- a/data/2026-05-04/BallparkPal_Teams.xlsx
+++ b/data/2026-05-04/BallparkPal_Teams.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>GamePk</t>
   </si>
@@ -162,6 +162,87 @@
   </si>
   <si>
     <t>RunsInningExtra</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -501,7 +582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AW1"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:49">
@@ -651,6 +732,3582 @@
       </c>
       <c r="AW1" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49">
+      <c r="A2">
+        <v>822984</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2">
+        <v>4.169</v>
+      </c>
+      <c r="G2">
+        <v>0.481</v>
+      </c>
+      <c r="H2">
+        <v>0.105</v>
+      </c>
+      <c r="I2">
+        <v>0.246</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>0.236</v>
+      </c>
+      <c r="L2">
+        <v>1.219</v>
+      </c>
+      <c r="M2">
+        <v>0.106</v>
+      </c>
+      <c r="N2">
+        <v>1.612</v>
+      </c>
+      <c r="O2">
+        <v>5.254</v>
+      </c>
+      <c r="P2">
+        <v>2.258</v>
+      </c>
+      <c r="Q2">
+        <v>7.531</v>
+      </c>
+      <c r="R2">
+        <v>0.289</v>
+      </c>
+      <c r="S2">
+        <v>0.371</v>
+      </c>
+      <c r="T2">
+        <v>0.223</v>
+      </c>
+      <c r="U2">
+        <v>0.083</v>
+      </c>
+      <c r="V2">
+        <v>0.024</v>
+      </c>
+      <c r="W2">
+        <v>0.011</v>
+      </c>
+      <c r="X2">
+        <v>0.056</v>
+      </c>
+      <c r="Y2">
+        <v>0.112</v>
+      </c>
+      <c r="Z2">
+        <v>0.147</v>
+      </c>
+      <c r="AA2">
+        <v>0.147</v>
+      </c>
+      <c r="AB2">
+        <v>0.135</v>
+      </c>
+      <c r="AC2">
+        <v>0.129</v>
+      </c>
+      <c r="AD2">
+        <v>0.09</v>
+      </c>
+      <c r="AE2">
+        <v>0.065</v>
+      </c>
+      <c r="AF2">
+        <v>0.047</v>
+      </c>
+      <c r="AG2">
+        <v>0.024</v>
+      </c>
+      <c r="AH2">
+        <v>0.019</v>
+      </c>
+      <c r="AI2">
+        <v>0.014</v>
+      </c>
+      <c r="AJ2">
+        <v>0.007</v>
+      </c>
+      <c r="AK2">
+        <v>0.003</v>
+      </c>
+      <c r="AL2">
+        <v>0.002</v>
+      </c>
+      <c r="AM2">
+        <v>0.003</v>
+      </c>
+      <c r="AN2">
+        <v>0.507</v>
+      </c>
+      <c r="AO2">
+        <v>0.4</v>
+      </c>
+      <c r="AP2">
+        <v>0.457</v>
+      </c>
+      <c r="AQ2">
+        <v>0.445</v>
+      </c>
+      <c r="AR2">
+        <v>0.421</v>
+      </c>
+      <c r="AS2">
+        <v>0.441</v>
+      </c>
+      <c r="AT2">
+        <v>0.443</v>
+      </c>
+      <c r="AU2">
+        <v>0.413</v>
+      </c>
+      <c r="AV2">
+        <v>0.406</v>
+      </c>
+      <c r="AW2">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49">
+      <c r="A3">
+        <v>823064</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <v>5.345</v>
+      </c>
+      <c r="G3">
+        <v>0.533</v>
+      </c>
+      <c r="H3">
+        <v>0.1</v>
+      </c>
+      <c r="I3">
+        <v>0.318</v>
+      </c>
+      <c r="J3">
+        <v>0.097</v>
+      </c>
+      <c r="K3">
+        <v>0.21</v>
+      </c>
+      <c r="L3">
+        <v>1.0</v>
+      </c>
+      <c r="M3">
+        <v>0.118</v>
+      </c>
+      <c r="N3">
+        <v>1.708</v>
+      </c>
+      <c r="O3">
+        <v>6.923</v>
+      </c>
+      <c r="P3">
+        <v>3.775</v>
+      </c>
+      <c r="Q3">
+        <v>7.25</v>
+      </c>
+      <c r="R3">
+        <v>0.37</v>
+      </c>
+      <c r="S3">
+        <v>0.362</v>
+      </c>
+      <c r="T3">
+        <v>0.189</v>
+      </c>
+      <c r="U3">
+        <v>0.059</v>
+      </c>
+      <c r="V3">
+        <v>0.016</v>
+      </c>
+      <c r="W3">
+        <v>0.003</v>
+      </c>
+      <c r="X3">
+        <v>0.033</v>
+      </c>
+      <c r="Y3">
+        <v>0.07</v>
+      </c>
+      <c r="Z3">
+        <v>0.098</v>
+      </c>
+      <c r="AA3">
+        <v>0.123</v>
+      </c>
+      <c r="AB3">
+        <v>0.13</v>
+      </c>
+      <c r="AC3">
+        <v>0.123</v>
+      </c>
+      <c r="AD3">
+        <v>0.109</v>
+      </c>
+      <c r="AE3">
+        <v>0.081</v>
+      </c>
+      <c r="AF3">
+        <v>0.074</v>
+      </c>
+      <c r="AG3">
+        <v>0.05</v>
+      </c>
+      <c r="AH3">
+        <v>0.034</v>
+      </c>
+      <c r="AI3">
+        <v>0.025</v>
+      </c>
+      <c r="AJ3">
+        <v>0.015</v>
+      </c>
+      <c r="AK3">
+        <v>0.011</v>
+      </c>
+      <c r="AL3">
+        <v>0.011</v>
+      </c>
+      <c r="AM3">
+        <v>0.013</v>
+      </c>
+      <c r="AN3">
+        <v>0.625</v>
+      </c>
+      <c r="AO3">
+        <v>0.554</v>
+      </c>
+      <c r="AP3">
+        <v>0.61</v>
+      </c>
+      <c r="AQ3">
+        <v>0.56</v>
+      </c>
+      <c r="AR3">
+        <v>0.594</v>
+      </c>
+      <c r="AS3">
+        <v>0.558</v>
+      </c>
+      <c r="AT3">
+        <v>0.531</v>
+      </c>
+      <c r="AU3">
+        <v>0.52</v>
+      </c>
+      <c r="AV3">
+        <v>0.503</v>
+      </c>
+      <c r="AW3">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49">
+      <c r="A4">
+        <v>823143</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4">
+        <v>4.163</v>
+      </c>
+      <c r="G4">
+        <v>0.419</v>
+      </c>
+      <c r="H4">
+        <v>0.087</v>
+      </c>
+      <c r="I4">
+        <v>0.214</v>
+      </c>
+      <c r="J4">
+        <v>0.108</v>
+      </c>
+      <c r="K4">
+        <v>0.301</v>
+      </c>
+      <c r="L4">
+        <v>1.258</v>
+      </c>
+      <c r="M4">
+        <v>0.126</v>
+      </c>
+      <c r="N4">
+        <v>1.546</v>
+      </c>
+      <c r="O4">
+        <v>5.527</v>
+      </c>
+      <c r="P4">
+        <v>2.304</v>
+      </c>
+      <c r="Q4">
+        <v>9.138</v>
+      </c>
+      <c r="R4">
+        <v>0.301</v>
+      </c>
+      <c r="S4">
+        <v>0.332</v>
+      </c>
+      <c r="T4">
+        <v>0.227</v>
+      </c>
+      <c r="U4">
+        <v>0.099</v>
+      </c>
+      <c r="V4">
+        <v>0.03</v>
+      </c>
+      <c r="W4">
+        <v>0.01</v>
+      </c>
+      <c r="X4">
+        <v>0.066</v>
+      </c>
+      <c r="Y4">
+        <v>0.117</v>
+      </c>
+      <c r="Z4">
+        <v>0.143</v>
+      </c>
+      <c r="AA4">
+        <v>0.147</v>
+      </c>
+      <c r="AB4">
+        <v>0.126</v>
+      </c>
+      <c r="AC4">
+        <v>0.115</v>
+      </c>
+      <c r="AD4">
+        <v>0.09</v>
+      </c>
+      <c r="AE4">
+        <v>0.062</v>
+      </c>
+      <c r="AF4">
+        <v>0.054</v>
+      </c>
+      <c r="AG4">
+        <v>0.036</v>
+      </c>
+      <c r="AH4">
+        <v>0.015</v>
+      </c>
+      <c r="AI4">
+        <v>0.01</v>
+      </c>
+      <c r="AJ4">
+        <v>0.01</v>
+      </c>
+      <c r="AK4">
+        <v>0.004</v>
+      </c>
+      <c r="AL4">
+        <v>0.003</v>
+      </c>
+      <c r="AM4">
+        <v>0.002</v>
+      </c>
+      <c r="AN4">
+        <v>0.47</v>
+      </c>
+      <c r="AO4">
+        <v>0.424</v>
+      </c>
+      <c r="AP4">
+        <v>0.477</v>
+      </c>
+      <c r="AQ4">
+        <v>0.441</v>
+      </c>
+      <c r="AR4">
+        <v>0.474</v>
+      </c>
+      <c r="AS4">
+        <v>0.408</v>
+      </c>
+      <c r="AT4">
+        <v>0.42</v>
+      </c>
+      <c r="AU4">
+        <v>0.429</v>
+      </c>
+      <c r="AV4">
+        <v>0.405</v>
+      </c>
+      <c r="AW4">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49">
+      <c r="A5">
+        <v>823228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5">
+        <v>4.419</v>
+      </c>
+      <c r="G5">
+        <v>0.531</v>
+      </c>
+      <c r="H5">
+        <v>0.095</v>
+      </c>
+      <c r="I5">
+        <v>0.301</v>
+      </c>
+      <c r="J5">
+        <v>0.094</v>
+      </c>
+      <c r="K5">
+        <v>0.2</v>
+      </c>
+      <c r="L5">
+        <v>0.803</v>
+      </c>
+      <c r="M5">
+        <v>0.13</v>
+      </c>
+      <c r="N5">
+        <v>1.685</v>
+      </c>
+      <c r="O5">
+        <v>6.491</v>
+      </c>
+      <c r="P5">
+        <v>2.872</v>
+      </c>
+      <c r="Q5">
+        <v>7.84</v>
+      </c>
+      <c r="R5">
+        <v>0.454</v>
+      </c>
+      <c r="S5">
+        <v>0.354</v>
+      </c>
+      <c r="T5">
+        <v>0.14</v>
+      </c>
+      <c r="U5">
+        <v>0.041</v>
+      </c>
+      <c r="V5">
+        <v>0.008</v>
+      </c>
+      <c r="W5">
+        <v>0.002</v>
+      </c>
+      <c r="X5">
+        <v>0.06</v>
+      </c>
+      <c r="Y5">
+        <v>0.112</v>
+      </c>
+      <c r="Z5">
+        <v>0.139</v>
+      </c>
+      <c r="AA5">
+        <v>0.124</v>
+      </c>
+      <c r="AB5">
+        <v>0.13</v>
+      </c>
+      <c r="AC5">
+        <v>0.118</v>
+      </c>
+      <c r="AD5">
+        <v>0.093</v>
+      </c>
+      <c r="AE5">
+        <v>0.069</v>
+      </c>
+      <c r="AF5">
+        <v>0.045</v>
+      </c>
+      <c r="AG5">
+        <v>0.043</v>
+      </c>
+      <c r="AH5">
+        <v>0.027</v>
+      </c>
+      <c r="AI5">
+        <v>0.017</v>
+      </c>
+      <c r="AJ5">
+        <v>0.008</v>
+      </c>
+      <c r="AK5">
+        <v>0.005</v>
+      </c>
+      <c r="AL5">
+        <v>0.004</v>
+      </c>
+      <c r="AM5">
+        <v>0.006</v>
+      </c>
+      <c r="AN5">
+        <v>0.425</v>
+      </c>
+      <c r="AO5">
+        <v>0.41</v>
+      </c>
+      <c r="AP5">
+        <v>0.425</v>
+      </c>
+      <c r="AQ5">
+        <v>0.442</v>
+      </c>
+      <c r="AR5">
+        <v>0.453</v>
+      </c>
+      <c r="AS5">
+        <v>0.465</v>
+      </c>
+      <c r="AT5">
+        <v>0.504</v>
+      </c>
+      <c r="AU5">
+        <v>0.496</v>
+      </c>
+      <c r="AV5">
+        <v>0.519</v>
+      </c>
+      <c r="AW5">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49">
+      <c r="A6">
+        <v>823552</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>3.535</v>
+      </c>
+      <c r="G6">
+        <v>0.285</v>
+      </c>
+      <c r="H6">
+        <v>0.061</v>
+      </c>
+      <c r="I6">
+        <v>0.137</v>
+      </c>
+      <c r="J6">
+        <v>0.121</v>
+      </c>
+      <c r="K6">
+        <v>0.433</v>
+      </c>
+      <c r="L6">
+        <v>1.088</v>
+      </c>
+      <c r="M6">
+        <v>0.094</v>
+      </c>
+      <c r="N6">
+        <v>1.378</v>
+      </c>
+      <c r="O6">
+        <v>4.655</v>
+      </c>
+      <c r="P6">
+        <v>2.374</v>
+      </c>
+      <c r="Q6">
+        <v>10.195</v>
+      </c>
+      <c r="R6">
+        <v>0.354</v>
+      </c>
+      <c r="S6">
+        <v>0.35</v>
+      </c>
+      <c r="T6">
+        <v>0.189</v>
+      </c>
+      <c r="U6">
+        <v>0.08</v>
+      </c>
+      <c r="V6">
+        <v>0.02</v>
+      </c>
+      <c r="W6">
+        <v>0.008</v>
+      </c>
+      <c r="X6">
+        <v>0.101</v>
+      </c>
+      <c r="Y6">
+        <v>0.152</v>
+      </c>
+      <c r="Z6">
+        <v>0.165</v>
+      </c>
+      <c r="AA6">
+        <v>0.151</v>
+      </c>
+      <c r="AB6">
+        <v>0.127</v>
+      </c>
+      <c r="AC6">
+        <v>0.102</v>
+      </c>
+      <c r="AD6">
+        <v>0.068</v>
+      </c>
+      <c r="AE6">
+        <v>0.046</v>
+      </c>
+      <c r="AF6">
+        <v>0.031</v>
+      </c>
+      <c r="AG6">
+        <v>0.023</v>
+      </c>
+      <c r="AH6">
+        <v>0.016</v>
+      </c>
+      <c r="AI6">
+        <v>0.008</v>
+      </c>
+      <c r="AJ6">
+        <v>0.005</v>
+      </c>
+      <c r="AK6">
+        <v>0.002</v>
+      </c>
+      <c r="AL6">
+        <v>0.003</v>
+      </c>
+      <c r="AM6">
+        <v>0.002</v>
+      </c>
+      <c r="AN6">
+        <v>0.322</v>
+      </c>
+      <c r="AO6">
+        <v>0.283</v>
+      </c>
+      <c r="AP6">
+        <v>0.326</v>
+      </c>
+      <c r="AQ6">
+        <v>0.314</v>
+      </c>
+      <c r="AR6">
+        <v>0.337</v>
+      </c>
+      <c r="AS6">
+        <v>0.355</v>
+      </c>
+      <c r="AT6">
+        <v>0.399</v>
+      </c>
+      <c r="AU6">
+        <v>0.491</v>
+      </c>
+      <c r="AV6">
+        <v>0.506</v>
+      </c>
+      <c r="AW6">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49">
+      <c r="A7">
+        <v>823874</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7">
+        <v>4.453</v>
+      </c>
+      <c r="G7">
+        <v>0.569</v>
+      </c>
+      <c r="H7">
+        <v>0.102</v>
+      </c>
+      <c r="I7">
+        <v>0.322</v>
+      </c>
+      <c r="J7">
+        <v>0.088</v>
+      </c>
+      <c r="K7">
+        <v>0.178</v>
+      </c>
+      <c r="L7">
+        <v>1.049</v>
+      </c>
+      <c r="M7">
+        <v>0.16</v>
+      </c>
+      <c r="N7">
+        <v>1.738</v>
+      </c>
+      <c r="O7">
+        <v>5.834</v>
+      </c>
+      <c r="P7">
+        <v>2.443</v>
+      </c>
+      <c r="Q7">
+        <v>6.663</v>
+      </c>
+      <c r="R7">
+        <v>0.352</v>
+      </c>
+      <c r="S7">
+        <v>0.368</v>
+      </c>
+      <c r="T7">
+        <v>0.189</v>
+      </c>
+      <c r="U7">
+        <v>0.066</v>
+      </c>
+      <c r="V7">
+        <v>0.018</v>
+      </c>
+      <c r="W7">
+        <v>0.006</v>
+      </c>
+      <c r="X7">
+        <v>0.057</v>
+      </c>
+      <c r="Y7">
+        <v>0.097</v>
+      </c>
+      <c r="Z7">
+        <v>0.129</v>
+      </c>
+      <c r="AA7">
+        <v>0.141</v>
+      </c>
+      <c r="AB7">
+        <v>0.135</v>
+      </c>
+      <c r="AC7">
+        <v>0.112</v>
+      </c>
+      <c r="AD7">
+        <v>0.096</v>
+      </c>
+      <c r="AE7">
+        <v>0.083</v>
+      </c>
+      <c r="AF7">
+        <v>0.062</v>
+      </c>
+      <c r="AG7">
+        <v>0.03</v>
+      </c>
+      <c r="AH7">
+        <v>0.025</v>
+      </c>
+      <c r="AI7">
+        <v>0.017</v>
+      </c>
+      <c r="AJ7">
+        <v>0.006</v>
+      </c>
+      <c r="AK7">
+        <v>0.004</v>
+      </c>
+      <c r="AL7">
+        <v>0.003</v>
+      </c>
+      <c r="AM7">
+        <v>0.003</v>
+      </c>
+      <c r="AN7">
+        <v>0.5</v>
+      </c>
+      <c r="AO7">
+        <v>0.486</v>
+      </c>
+      <c r="AP7">
+        <v>0.497</v>
+      </c>
+      <c r="AQ7">
+        <v>0.463</v>
+      </c>
+      <c r="AR7">
+        <v>0.426</v>
+      </c>
+      <c r="AS7">
+        <v>0.446</v>
+      </c>
+      <c r="AT7">
+        <v>0.47</v>
+      </c>
+      <c r="AU7">
+        <v>0.454</v>
+      </c>
+      <c r="AV7">
+        <v>0.462</v>
+      </c>
+      <c r="AW7">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49">
+      <c r="A8">
+        <v>824039</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8">
+        <v>4.166</v>
+      </c>
+      <c r="G8">
+        <v>0.39</v>
+      </c>
+      <c r="H8">
+        <v>0.081</v>
+      </c>
+      <c r="I8">
+        <v>0.203</v>
+      </c>
+      <c r="J8">
+        <v>0.105</v>
+      </c>
+      <c r="K8">
+        <v>0.331</v>
+      </c>
+      <c r="L8">
+        <v>0.895</v>
+      </c>
+      <c r="M8">
+        <v>0.081</v>
+      </c>
+      <c r="N8">
+        <v>1.424</v>
+      </c>
+      <c r="O8">
+        <v>5.319</v>
+      </c>
+      <c r="P8">
+        <v>4.163</v>
+      </c>
+      <c r="Q8">
+        <v>10.574</v>
+      </c>
+      <c r="R8">
+        <v>0.423</v>
+      </c>
+      <c r="S8">
+        <v>0.348</v>
+      </c>
+      <c r="T8">
+        <v>0.16</v>
+      </c>
+      <c r="U8">
+        <v>0.054</v>
+      </c>
+      <c r="V8">
+        <v>0.012</v>
+      </c>
+      <c r="W8">
+        <v>0.003</v>
+      </c>
+      <c r="X8">
+        <v>0.082</v>
+      </c>
+      <c r="Y8">
+        <v>0.121</v>
+      </c>
+      <c r="Z8">
+        <v>0.134</v>
+      </c>
+      <c r="AA8">
+        <v>0.14</v>
+      </c>
+      <c r="AB8">
+        <v>0.129</v>
+      </c>
+      <c r="AC8">
+        <v>0.103</v>
+      </c>
+      <c r="AD8">
+        <v>0.091</v>
+      </c>
+      <c r="AE8">
+        <v>0.062</v>
+      </c>
+      <c r="AF8">
+        <v>0.042</v>
+      </c>
+      <c r="AG8">
+        <v>0.035</v>
+      </c>
+      <c r="AH8">
+        <v>0.021</v>
+      </c>
+      <c r="AI8">
+        <v>0.014</v>
+      </c>
+      <c r="AJ8">
+        <v>0.012</v>
+      </c>
+      <c r="AK8">
+        <v>0.005</v>
+      </c>
+      <c r="AL8">
+        <v>0.004</v>
+      </c>
+      <c r="AM8">
+        <v>0.004</v>
+      </c>
+      <c r="AN8">
+        <v>0.455</v>
+      </c>
+      <c r="AO8">
+        <v>0.346</v>
+      </c>
+      <c r="AP8">
+        <v>0.398</v>
+      </c>
+      <c r="AQ8">
+        <v>0.362</v>
+      </c>
+      <c r="AR8">
+        <v>0.405</v>
+      </c>
+      <c r="AS8">
+        <v>0.395</v>
+      </c>
+      <c r="AT8">
+        <v>0.485</v>
+      </c>
+      <c r="AU8">
+        <v>0.547</v>
+      </c>
+      <c r="AV8">
+        <v>0.52</v>
+      </c>
+      <c r="AW8">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49">
+      <c r="A9">
+        <v>824120</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9">
+        <v>5.243</v>
+      </c>
+      <c r="G9">
+        <v>0.454</v>
+      </c>
+      <c r="H9">
+        <v>0.084</v>
+      </c>
+      <c r="I9">
+        <v>0.259</v>
+      </c>
+      <c r="J9">
+        <v>0.106</v>
+      </c>
+      <c r="K9">
+        <v>0.282</v>
+      </c>
+      <c r="L9">
+        <v>1.414</v>
+      </c>
+      <c r="M9">
+        <v>0.107</v>
+      </c>
+      <c r="N9">
+        <v>1.89</v>
+      </c>
+      <c r="O9">
+        <v>5.574</v>
+      </c>
+      <c r="P9">
+        <v>3.335</v>
+      </c>
+      <c r="Q9">
+        <v>6.466</v>
+      </c>
+      <c r="R9">
+        <v>0.244</v>
+      </c>
+      <c r="S9">
+        <v>0.352</v>
+      </c>
+      <c r="T9">
+        <v>0.232</v>
+      </c>
+      <c r="U9">
+        <v>0.11</v>
+      </c>
+      <c r="V9">
+        <v>0.045</v>
+      </c>
+      <c r="W9">
+        <v>0.017</v>
+      </c>
+      <c r="X9">
+        <v>0.033</v>
+      </c>
+      <c r="Y9">
+        <v>0.074</v>
+      </c>
+      <c r="Z9">
+        <v>0.114</v>
+      </c>
+      <c r="AA9">
+        <v>0.118</v>
+      </c>
+      <c r="AB9">
+        <v>0.134</v>
+      </c>
+      <c r="AC9">
+        <v>0.116</v>
+      </c>
+      <c r="AD9">
+        <v>0.092</v>
+      </c>
+      <c r="AE9">
+        <v>0.093</v>
+      </c>
+      <c r="AF9">
+        <v>0.063</v>
+      </c>
+      <c r="AG9">
+        <v>0.053</v>
+      </c>
+      <c r="AH9">
+        <v>0.043</v>
+      </c>
+      <c r="AI9">
+        <v>0.023</v>
+      </c>
+      <c r="AJ9">
+        <v>0.017</v>
+      </c>
+      <c r="AK9">
+        <v>0.009</v>
+      </c>
+      <c r="AL9">
+        <v>0.006</v>
+      </c>
+      <c r="AM9">
+        <v>0.012</v>
+      </c>
+      <c r="AN9">
+        <v>0.561</v>
+      </c>
+      <c r="AO9">
+        <v>0.495</v>
+      </c>
+      <c r="AP9">
+        <v>0.559</v>
+      </c>
+      <c r="AQ9">
+        <v>0.566</v>
+      </c>
+      <c r="AR9">
+        <v>0.525</v>
+      </c>
+      <c r="AS9">
+        <v>0.568</v>
+      </c>
+      <c r="AT9">
+        <v>0.553</v>
+      </c>
+      <c r="AU9">
+        <v>0.568</v>
+      </c>
+      <c r="AV9">
+        <v>0.585</v>
+      </c>
+      <c r="AW9">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49">
+      <c r="A10">
+        <v>824201</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <v>5.165</v>
+      </c>
+      <c r="G10">
+        <v>0.586</v>
+      </c>
+      <c r="H10">
+        <v>0.103</v>
+      </c>
+      <c r="I10">
+        <v>0.36</v>
+      </c>
+      <c r="J10">
+        <v>0.086</v>
+      </c>
+      <c r="K10">
+        <v>0.174</v>
+      </c>
+      <c r="L10">
+        <v>1.392</v>
+      </c>
+      <c r="M10">
+        <v>0.127</v>
+      </c>
+      <c r="N10">
+        <v>1.503</v>
+      </c>
+      <c r="O10">
+        <v>5.505</v>
+      </c>
+      <c r="P10">
+        <v>4.499</v>
+      </c>
+      <c r="Q10">
+        <v>8.845</v>
+      </c>
+      <c r="R10">
+        <v>0.244</v>
+      </c>
+      <c r="S10">
+        <v>0.362</v>
+      </c>
+      <c r="T10">
+        <v>0.233</v>
+      </c>
+      <c r="U10">
+        <v>0.103</v>
+      </c>
+      <c r="V10">
+        <v>0.04</v>
+      </c>
+      <c r="W10">
+        <v>0.018</v>
+      </c>
+      <c r="X10">
+        <v>0.036</v>
+      </c>
+      <c r="Y10">
+        <v>0.091</v>
+      </c>
+      <c r="Z10">
+        <v>0.101</v>
+      </c>
+      <c r="AA10">
+        <v>0.121</v>
+      </c>
+      <c r="AB10">
+        <v>0.119</v>
+      </c>
+      <c r="AC10">
+        <v>0.112</v>
+      </c>
+      <c r="AD10">
+        <v>0.11</v>
+      </c>
+      <c r="AE10">
+        <v>0.086</v>
+      </c>
+      <c r="AF10">
+        <v>0.074</v>
+      </c>
+      <c r="AG10">
+        <v>0.051</v>
+      </c>
+      <c r="AH10">
+        <v>0.037</v>
+      </c>
+      <c r="AI10">
+        <v>0.021</v>
+      </c>
+      <c r="AJ10">
+        <v>0.014</v>
+      </c>
+      <c r="AK10">
+        <v>0.014</v>
+      </c>
+      <c r="AL10">
+        <v>0.006</v>
+      </c>
+      <c r="AM10">
+        <v>0.008</v>
+      </c>
+      <c r="AN10">
+        <v>0.534</v>
+      </c>
+      <c r="AO10">
+        <v>0.498</v>
+      </c>
+      <c r="AP10">
+        <v>0.56</v>
+      </c>
+      <c r="AQ10">
+        <v>0.576</v>
+      </c>
+      <c r="AR10">
+        <v>0.553</v>
+      </c>
+      <c r="AS10">
+        <v>0.573</v>
+      </c>
+      <c r="AT10">
+        <v>0.544</v>
+      </c>
+      <c r="AU10">
+        <v>0.569</v>
+      </c>
+      <c r="AV10">
+        <v>0.498</v>
+      </c>
+      <c r="AW10">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49">
+      <c r="A11">
+        <v>824283</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11">
+        <v>4.177</v>
+      </c>
+      <c r="G11">
+        <v>0.365</v>
+      </c>
+      <c r="H11">
+        <v>0.084</v>
+      </c>
+      <c r="I11">
+        <v>0.178</v>
+      </c>
+      <c r="J11">
+        <v>0.107</v>
+      </c>
+      <c r="K11">
+        <v>0.358</v>
+      </c>
+      <c r="L11">
+        <v>0.77</v>
+      </c>
+      <c r="M11">
+        <v>0.115</v>
+      </c>
+      <c r="N11">
+        <v>1.62</v>
+      </c>
+      <c r="O11">
+        <v>6.603</v>
+      </c>
+      <c r="P11">
+        <v>2.233</v>
+      </c>
+      <c r="Q11">
+        <v>9.563</v>
+      </c>
+      <c r="R11">
+        <v>0.47</v>
+      </c>
+      <c r="S11">
+        <v>0.348</v>
+      </c>
+      <c r="T11">
+        <v>0.138</v>
+      </c>
+      <c r="U11">
+        <v>0.035</v>
+      </c>
+      <c r="V11">
+        <v>0.005</v>
+      </c>
+      <c r="W11">
+        <v>0.004</v>
+      </c>
+      <c r="X11">
+        <v>0.07</v>
+      </c>
+      <c r="Y11">
+        <v>0.123</v>
+      </c>
+      <c r="Z11">
+        <v>0.139</v>
+      </c>
+      <c r="AA11">
+        <v>0.14</v>
+      </c>
+      <c r="AB11">
+        <v>0.133</v>
+      </c>
+      <c r="AC11">
+        <v>0.108</v>
+      </c>
+      <c r="AD11">
+        <v>0.087</v>
+      </c>
+      <c r="AE11">
+        <v>0.068</v>
+      </c>
+      <c r="AF11">
+        <v>0.046</v>
+      </c>
+      <c r="AG11">
+        <v>0.03</v>
+      </c>
+      <c r="AH11">
+        <v>0.019</v>
+      </c>
+      <c r="AI11">
+        <v>0.013</v>
+      </c>
+      <c r="AJ11">
+        <v>0.008</v>
+      </c>
+      <c r="AK11">
+        <v>0.007</v>
+      </c>
+      <c r="AL11">
+        <v>0.003</v>
+      </c>
+      <c r="AM11">
+        <v>0.005</v>
+      </c>
+      <c r="AN11">
+        <v>0.433</v>
+      </c>
+      <c r="AO11">
+        <v>0.372</v>
+      </c>
+      <c r="AP11">
+        <v>0.414</v>
+      </c>
+      <c r="AQ11">
+        <v>0.453</v>
+      </c>
+      <c r="AR11">
+        <v>0.428</v>
+      </c>
+      <c r="AS11">
+        <v>0.439</v>
+      </c>
+      <c r="AT11">
+        <v>0.455</v>
+      </c>
+      <c r="AU11">
+        <v>0.456</v>
+      </c>
+      <c r="AV11">
+        <v>0.483</v>
+      </c>
+      <c r="AW11">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49">
+      <c r="A12">
+        <v>824363</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12">
+        <v>6.334</v>
+      </c>
+      <c r="G12">
+        <v>0.474</v>
+      </c>
+      <c r="H12">
+        <v>0.078</v>
+      </c>
+      <c r="I12">
+        <v>0.299</v>
+      </c>
+      <c r="J12">
+        <v>0.091</v>
+      </c>
+      <c r="K12">
+        <v>0.3</v>
+      </c>
+      <c r="L12">
+        <v>1.549</v>
+      </c>
+      <c r="M12">
+        <v>0.144</v>
+      </c>
+      <c r="N12">
+        <v>2.284</v>
+      </c>
+      <c r="O12">
+        <v>6.537</v>
+      </c>
+      <c r="P12">
+        <v>3.543</v>
+      </c>
+      <c r="Q12">
+        <v>6.423</v>
+      </c>
+      <c r="R12">
+        <v>0.227</v>
+      </c>
+      <c r="S12">
+        <v>0.315</v>
+      </c>
+      <c r="T12">
+        <v>0.244</v>
+      </c>
+      <c r="U12">
+        <v>0.138</v>
+      </c>
+      <c r="V12">
+        <v>0.054</v>
+      </c>
+      <c r="W12">
+        <v>0.022</v>
+      </c>
+      <c r="X12">
+        <v>0.022</v>
+      </c>
+      <c r="Y12">
+        <v>0.055</v>
+      </c>
+      <c r="Z12">
+        <v>0.073</v>
+      </c>
+      <c r="AA12">
+        <v>0.093</v>
+      </c>
+      <c r="AB12">
+        <v>0.113</v>
+      </c>
+      <c r="AC12">
+        <v>0.103</v>
+      </c>
+      <c r="AD12">
+        <v>0.097</v>
+      </c>
+      <c r="AE12">
+        <v>0.102</v>
+      </c>
+      <c r="AF12">
+        <v>0.082</v>
+      </c>
+      <c r="AG12">
+        <v>0.075</v>
+      </c>
+      <c r="AH12">
+        <v>0.054</v>
+      </c>
+      <c r="AI12">
+        <v>0.041</v>
+      </c>
+      <c r="AJ12">
+        <v>0.03</v>
+      </c>
+      <c r="AK12">
+        <v>0.022</v>
+      </c>
+      <c r="AL12">
+        <v>0.012</v>
+      </c>
+      <c r="AM12">
+        <v>0.027</v>
+      </c>
+      <c r="AN12">
+        <v>0.719</v>
+      </c>
+      <c r="AO12">
+        <v>0.641</v>
+      </c>
+      <c r="AP12">
+        <v>0.692</v>
+      </c>
+      <c r="AQ12">
+        <v>0.661</v>
+      </c>
+      <c r="AR12">
+        <v>0.66</v>
+      </c>
+      <c r="AS12">
+        <v>0.654</v>
+      </c>
+      <c r="AT12">
+        <v>0.673</v>
+      </c>
+      <c r="AU12">
+        <v>0.67</v>
+      </c>
+      <c r="AV12">
+        <v>0.669</v>
+      </c>
+      <c r="AW12">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49">
+      <c r="A13">
+        <v>824684</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13">
+        <v>5.968</v>
+      </c>
+      <c r="G13">
+        <v>0.356</v>
+      </c>
+      <c r="H13">
+        <v>0.065</v>
+      </c>
+      <c r="I13">
+        <v>0.205</v>
+      </c>
+      <c r="J13">
+        <v>0.091</v>
+      </c>
+      <c r="K13">
+        <v>0.41</v>
+      </c>
+      <c r="L13">
+        <v>1.768</v>
+      </c>
+      <c r="M13">
+        <v>0.2</v>
+      </c>
+      <c r="N13">
+        <v>1.882</v>
+      </c>
+      <c r="O13">
+        <v>5.339</v>
+      </c>
+      <c r="P13">
+        <v>4.347</v>
+      </c>
+      <c r="Q13">
+        <v>9.65</v>
+      </c>
+      <c r="R13">
+        <v>0.19</v>
+      </c>
+      <c r="S13">
+        <v>0.286</v>
+      </c>
+      <c r="T13">
+        <v>0.258</v>
+      </c>
+      <c r="U13">
+        <v>0.157</v>
+      </c>
+      <c r="V13">
+        <v>0.067</v>
+      </c>
+      <c r="W13">
+        <v>0.041</v>
+      </c>
+      <c r="X13">
+        <v>0.026</v>
+      </c>
+      <c r="Y13">
+        <v>0.055</v>
+      </c>
+      <c r="Z13">
+        <v>0.086</v>
+      </c>
+      <c r="AA13">
+        <v>0.11</v>
+      </c>
+      <c r="AB13">
+        <v>0.113</v>
+      </c>
+      <c r="AC13">
+        <v>0.109</v>
+      </c>
+      <c r="AD13">
+        <v>0.104</v>
+      </c>
+      <c r="AE13">
+        <v>0.102</v>
+      </c>
+      <c r="AF13">
+        <v>0.071</v>
+      </c>
+      <c r="AG13">
+        <v>0.065</v>
+      </c>
+      <c r="AH13">
+        <v>0.052</v>
+      </c>
+      <c r="AI13">
+        <v>0.034</v>
+      </c>
+      <c r="AJ13">
+        <v>0.025</v>
+      </c>
+      <c r="AK13">
+        <v>0.015</v>
+      </c>
+      <c r="AL13">
+        <v>0.014</v>
+      </c>
+      <c r="AM13">
+        <v>0.022</v>
+      </c>
+      <c r="AN13">
+        <v>0.657</v>
+      </c>
+      <c r="AO13">
+        <v>0.69</v>
+      </c>
+      <c r="AP13">
+        <v>0.638</v>
+      </c>
+      <c r="AQ13">
+        <v>0.608</v>
+      </c>
+      <c r="AR13">
+        <v>0.617</v>
+      </c>
+      <c r="AS13">
+        <v>0.611</v>
+      </c>
+      <c r="AT13">
+        <v>0.643</v>
+      </c>
+      <c r="AU13">
+        <v>0.611</v>
+      </c>
+      <c r="AV13">
+        <v>0.655</v>
+      </c>
+      <c r="AW13">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:49">
+      <c r="A14">
+        <v>822984</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14">
+        <v>4.161</v>
+      </c>
+      <c r="G14">
+        <v>0.519</v>
+      </c>
+      <c r="H14">
+        <v>0.1</v>
+      </c>
+      <c r="I14">
+        <v>0.236</v>
+      </c>
+      <c r="J14">
+        <v>0.105</v>
+      </c>
+      <c r="K14">
+        <v>0.246</v>
+      </c>
+      <c r="L14">
+        <v>0.863</v>
+      </c>
+      <c r="M14">
+        <v>0.115</v>
+      </c>
+      <c r="N14">
+        <v>1.817</v>
+      </c>
+      <c r="O14">
+        <v>5.457</v>
+      </c>
+      <c r="P14">
+        <v>2.679</v>
+      </c>
+      <c r="Q14">
+        <v>7.164</v>
+      </c>
+      <c r="R14">
+        <v>0.408</v>
+      </c>
+      <c r="S14">
+        <v>0.384</v>
+      </c>
+      <c r="T14">
+        <v>0.153</v>
+      </c>
+      <c r="U14">
+        <v>0.048</v>
+      </c>
+      <c r="V14">
+        <v>0.006</v>
+      </c>
+      <c r="W14">
+        <v>0.001</v>
+      </c>
+      <c r="X14">
+        <v>0.062</v>
+      </c>
+      <c r="Y14">
+        <v>0.101</v>
+      </c>
+      <c r="Z14">
+        <v>0.134</v>
+      </c>
+      <c r="AA14">
+        <v>0.155</v>
+      </c>
+      <c r="AB14">
+        <v>0.148</v>
+      </c>
+      <c r="AC14">
+        <v>0.119</v>
+      </c>
+      <c r="AD14">
+        <v>0.095</v>
+      </c>
+      <c r="AE14">
+        <v>0.069</v>
+      </c>
+      <c r="AF14">
+        <v>0.049</v>
+      </c>
+      <c r="AG14">
+        <v>0.028</v>
+      </c>
+      <c r="AH14">
+        <v>0.019</v>
+      </c>
+      <c r="AI14">
+        <v>0.01</v>
+      </c>
+      <c r="AJ14">
+        <v>0.004</v>
+      </c>
+      <c r="AK14">
+        <v>0.003</v>
+      </c>
+      <c r="AL14">
+        <v>0.001</v>
+      </c>
+      <c r="AM14">
+        <v>0.002</v>
+      </c>
+      <c r="AN14">
+        <v>0.567</v>
+      </c>
+      <c r="AO14">
+        <v>0.485</v>
+      </c>
+      <c r="AP14">
+        <v>0.548</v>
+      </c>
+      <c r="AQ14">
+        <v>0.456</v>
+      </c>
+      <c r="AR14">
+        <v>0.448</v>
+      </c>
+      <c r="AS14">
+        <v>0.422</v>
+      </c>
+      <c r="AT14">
+        <v>0.403</v>
+      </c>
+      <c r="AU14">
+        <v>0.405</v>
+      </c>
+      <c r="AV14">
+        <v>0.206</v>
+      </c>
+      <c r="AW14">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49">
+      <c r="A15">
+        <v>823064</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15">
+        <v>4.664</v>
+      </c>
+      <c r="G15">
+        <v>0.467</v>
+      </c>
+      <c r="H15">
+        <v>0.097</v>
+      </c>
+      <c r="I15">
+        <v>0.21</v>
+      </c>
+      <c r="J15">
+        <v>0.1</v>
+      </c>
+      <c r="K15">
+        <v>0.318</v>
+      </c>
+      <c r="L15">
+        <v>1.17</v>
+      </c>
+      <c r="M15">
+        <v>0.057</v>
+      </c>
+      <c r="N15">
+        <v>1.749</v>
+      </c>
+      <c r="O15">
+        <v>5.258</v>
+      </c>
+      <c r="P15">
+        <v>3.557</v>
+      </c>
+      <c r="Q15">
+        <v>8.247</v>
+      </c>
+      <c r="R15">
+        <v>0.32</v>
+      </c>
+      <c r="S15">
+        <v>0.35</v>
+      </c>
+      <c r="T15">
+        <v>0.217</v>
+      </c>
+      <c r="U15">
+        <v>0.081</v>
+      </c>
+      <c r="V15">
+        <v>0.021</v>
+      </c>
+      <c r="W15">
+        <v>0.011</v>
+      </c>
+      <c r="X15">
+        <v>0.048</v>
+      </c>
+      <c r="Y15">
+        <v>0.08</v>
+      </c>
+      <c r="Z15">
+        <v>0.121</v>
+      </c>
+      <c r="AA15">
+        <v>0.145</v>
+      </c>
+      <c r="AB15">
+        <v>0.139</v>
+      </c>
+      <c r="AC15">
+        <v>0.124</v>
+      </c>
+      <c r="AD15">
+        <v>0.101</v>
+      </c>
+      <c r="AE15">
+        <v>0.081</v>
+      </c>
+      <c r="AF15">
+        <v>0.053</v>
+      </c>
+      <c r="AG15">
+        <v>0.038</v>
+      </c>
+      <c r="AH15">
+        <v>0.025</v>
+      </c>
+      <c r="AI15">
+        <v>0.02</v>
+      </c>
+      <c r="AJ15">
+        <v>0.008</v>
+      </c>
+      <c r="AK15">
+        <v>0.007</v>
+      </c>
+      <c r="AL15">
+        <v>0.003</v>
+      </c>
+      <c r="AM15">
+        <v>0.005</v>
+      </c>
+      <c r="AN15">
+        <v>0.606</v>
+      </c>
+      <c r="AO15">
+        <v>0.525</v>
+      </c>
+      <c r="AP15">
+        <v>0.532</v>
+      </c>
+      <c r="AQ15">
+        <v>0.512</v>
+      </c>
+      <c r="AR15">
+        <v>0.528</v>
+      </c>
+      <c r="AS15">
+        <v>0.463</v>
+      </c>
+      <c r="AT15">
+        <v>0.502</v>
+      </c>
+      <c r="AU15">
+        <v>0.488</v>
+      </c>
+      <c r="AV15">
+        <v>0.288</v>
+      </c>
+      <c r="AW15">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49">
+      <c r="A16">
+        <v>823143</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16">
+        <v>4.721</v>
+      </c>
+      <c r="G16">
+        <v>0.581</v>
+      </c>
+      <c r="H16">
+        <v>0.108</v>
+      </c>
+      <c r="I16">
+        <v>0.301</v>
+      </c>
+      <c r="J16">
+        <v>0.087</v>
+      </c>
+      <c r="K16">
+        <v>0.214</v>
+      </c>
+      <c r="L16">
+        <v>1.349</v>
+      </c>
+      <c r="M16">
+        <v>0.091</v>
+      </c>
+      <c r="N16">
+        <v>1.57</v>
+      </c>
+      <c r="O16">
+        <v>4.931</v>
+      </c>
+      <c r="P16">
+        <v>3.952</v>
+      </c>
+      <c r="Q16">
+        <v>8.909</v>
+      </c>
+      <c r="R16">
+        <v>0.248</v>
+      </c>
+      <c r="S16">
+        <v>0.364</v>
+      </c>
+      <c r="T16">
+        <v>0.24</v>
+      </c>
+      <c r="U16">
+        <v>0.101</v>
+      </c>
+      <c r="V16">
+        <v>0.036</v>
+      </c>
+      <c r="W16">
+        <v>0.011</v>
+      </c>
+      <c r="X16">
+        <v>0.037</v>
+      </c>
+      <c r="Y16">
+        <v>0.086</v>
+      </c>
+      <c r="Z16">
+        <v>0.118</v>
+      </c>
+      <c r="AA16">
+        <v>0.135</v>
+      </c>
+      <c r="AB16">
+        <v>0.147</v>
+      </c>
+      <c r="AC16">
+        <v>0.126</v>
+      </c>
+      <c r="AD16">
+        <v>0.109</v>
+      </c>
+      <c r="AE16">
+        <v>0.081</v>
+      </c>
+      <c r="AF16">
+        <v>0.056</v>
+      </c>
+      <c r="AG16">
+        <v>0.04</v>
+      </c>
+      <c r="AH16">
+        <v>0.023</v>
+      </c>
+      <c r="AI16">
+        <v>0.018</v>
+      </c>
+      <c r="AJ16">
+        <v>0.011</v>
+      </c>
+      <c r="AK16">
+        <v>0.004</v>
+      </c>
+      <c r="AL16">
+        <v>0.002</v>
+      </c>
+      <c r="AM16">
+        <v>0.006</v>
+      </c>
+      <c r="AN16">
+        <v>0.61</v>
+      </c>
+      <c r="AO16">
+        <v>0.498</v>
+      </c>
+      <c r="AP16">
+        <v>0.552</v>
+      </c>
+      <c r="AQ16">
+        <v>0.555</v>
+      </c>
+      <c r="AR16">
+        <v>0.554</v>
+      </c>
+      <c r="AS16">
+        <v>0.506</v>
+      </c>
+      <c r="AT16">
+        <v>0.517</v>
+      </c>
+      <c r="AU16">
+        <v>0.503</v>
+      </c>
+      <c r="AV16">
+        <v>0.212</v>
+      </c>
+      <c r="AW16">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49">
+      <c r="A17">
+        <v>823228</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17">
+        <v>3.874</v>
+      </c>
+      <c r="G17">
+        <v>0.469</v>
+      </c>
+      <c r="H17">
+        <v>0.094</v>
+      </c>
+      <c r="I17">
+        <v>0.2</v>
+      </c>
+      <c r="J17">
+        <v>0.095</v>
+      </c>
+      <c r="K17">
+        <v>0.301</v>
+      </c>
+      <c r="L17">
+        <v>0.713</v>
+      </c>
+      <c r="M17">
+        <v>0.134</v>
+      </c>
+      <c r="N17">
+        <v>1.718</v>
+      </c>
+      <c r="O17">
+        <v>5.604</v>
+      </c>
+      <c r="P17">
+        <v>2.861</v>
+      </c>
+      <c r="Q17">
+        <v>7.332</v>
+      </c>
+      <c r="R17">
+        <v>0.493</v>
+      </c>
+      <c r="S17">
+        <v>0.347</v>
+      </c>
+      <c r="T17">
+        <v>0.122</v>
+      </c>
+      <c r="U17">
+        <v>0.029</v>
+      </c>
+      <c r="V17">
+        <v>0.008</v>
+      </c>
+      <c r="W17">
+        <v>0.0</v>
+      </c>
+      <c r="X17">
+        <v>0.084</v>
+      </c>
+      <c r="Y17">
+        <v>0.121</v>
+      </c>
+      <c r="Z17">
+        <v>0.147</v>
+      </c>
+      <c r="AA17">
+        <v>0.152</v>
+      </c>
+      <c r="AB17">
+        <v>0.138</v>
+      </c>
+      <c r="AC17">
+        <v>0.109</v>
+      </c>
+      <c r="AD17">
+        <v>0.09</v>
+      </c>
+      <c r="AE17">
+        <v>0.053</v>
+      </c>
+      <c r="AF17">
+        <v>0.041</v>
+      </c>
+      <c r="AG17">
+        <v>0.028</v>
+      </c>
+      <c r="AH17">
+        <v>0.015</v>
+      </c>
+      <c r="AI17">
+        <v>0.007</v>
+      </c>
+      <c r="AJ17">
+        <v>0.008</v>
+      </c>
+      <c r="AK17">
+        <v>0.002</v>
+      </c>
+      <c r="AL17">
+        <v>0.002</v>
+      </c>
+      <c r="AM17">
+        <v>0.002</v>
+      </c>
+      <c r="AN17">
+        <v>0.406</v>
+      </c>
+      <c r="AO17">
+        <v>0.428</v>
+      </c>
+      <c r="AP17">
+        <v>0.426</v>
+      </c>
+      <c r="AQ17">
+        <v>0.4</v>
+      </c>
+      <c r="AR17">
+        <v>0.422</v>
+      </c>
+      <c r="AS17">
+        <v>0.464</v>
+      </c>
+      <c r="AT17">
+        <v>0.46</v>
+      </c>
+      <c r="AU17">
+        <v>0.41</v>
+      </c>
+      <c r="AV17">
+        <v>0.232</v>
+      </c>
+      <c r="AW17">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49">
+      <c r="A18">
+        <v>823552</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18">
+        <v>5.562</v>
+      </c>
+      <c r="G18">
+        <v>0.715</v>
+      </c>
+      <c r="H18">
+        <v>0.121</v>
+      </c>
+      <c r="I18">
+        <v>0.433</v>
+      </c>
+      <c r="J18">
+        <v>0.061</v>
+      </c>
+      <c r="K18">
+        <v>0.137</v>
+      </c>
+      <c r="L18">
+        <v>1.37</v>
+      </c>
+      <c r="M18">
+        <v>0.108</v>
+      </c>
+      <c r="N18">
+        <v>1.542</v>
+      </c>
+      <c r="O18">
+        <v>5.424</v>
+      </c>
+      <c r="P18">
+        <v>5.074</v>
+      </c>
+      <c r="Q18">
+        <v>8.371</v>
+      </c>
+      <c r="R18">
+        <v>0.254</v>
+      </c>
+      <c r="S18">
+        <v>0.353</v>
+      </c>
+      <c r="T18">
+        <v>0.236</v>
+      </c>
+      <c r="U18">
+        <v>0.105</v>
+      </c>
+      <c r="V18">
+        <v>0.039</v>
+      </c>
+      <c r="W18">
+        <v>0.013</v>
+      </c>
+      <c r="X18">
+        <v>0.034</v>
+      </c>
+      <c r="Y18">
+        <v>0.055</v>
+      </c>
+      <c r="Z18">
+        <v>0.09</v>
+      </c>
+      <c r="AA18">
+        <v>0.118</v>
+      </c>
+      <c r="AB18">
+        <v>0.124</v>
+      </c>
+      <c r="AC18">
+        <v>0.126</v>
+      </c>
+      <c r="AD18">
+        <v>0.116</v>
+      </c>
+      <c r="AE18">
+        <v>0.089</v>
+      </c>
+      <c r="AF18">
+        <v>0.072</v>
+      </c>
+      <c r="AG18">
+        <v>0.054</v>
+      </c>
+      <c r="AH18">
+        <v>0.039</v>
+      </c>
+      <c r="AI18">
+        <v>0.026</v>
+      </c>
+      <c r="AJ18">
+        <v>0.02</v>
+      </c>
+      <c r="AK18">
+        <v>0.012</v>
+      </c>
+      <c r="AL18">
+        <v>0.009</v>
+      </c>
+      <c r="AM18">
+        <v>0.016</v>
+      </c>
+      <c r="AN18">
+        <v>0.725</v>
+      </c>
+      <c r="AO18">
+        <v>0.579</v>
+      </c>
+      <c r="AP18">
+        <v>0.688</v>
+      </c>
+      <c r="AQ18">
+        <v>0.632</v>
+      </c>
+      <c r="AR18">
+        <v>0.658</v>
+      </c>
+      <c r="AS18">
+        <v>0.606</v>
+      </c>
+      <c r="AT18">
+        <v>0.621</v>
+      </c>
+      <c r="AU18">
+        <v>0.635</v>
+      </c>
+      <c r="AV18">
+        <v>0.188</v>
+      </c>
+      <c r="AW18">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49">
+      <c r="A19">
+        <v>823874</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19">
+        <v>3.658</v>
+      </c>
+      <c r="G19">
+        <v>0.431</v>
+      </c>
+      <c r="H19">
+        <v>0.088</v>
+      </c>
+      <c r="I19">
+        <v>0.178</v>
+      </c>
+      <c r="J19">
+        <v>0.102</v>
+      </c>
+      <c r="K19">
+        <v>0.322</v>
+      </c>
+      <c r="L19">
+        <v>0.794</v>
+      </c>
+      <c r="M19">
+        <v>0.125</v>
+      </c>
+      <c r="N19">
+        <v>1.584</v>
+      </c>
+      <c r="O19">
+        <v>4.692</v>
+      </c>
+      <c r="P19">
+        <v>3.174</v>
+      </c>
+      <c r="Q19">
+        <v>8.652</v>
+      </c>
+      <c r="R19">
+        <v>0.45</v>
+      </c>
+      <c r="S19">
+        <v>0.361</v>
+      </c>
+      <c r="T19">
+        <v>0.143</v>
+      </c>
+      <c r="U19">
+        <v>0.039</v>
+      </c>
+      <c r="V19">
+        <v>0.005</v>
+      </c>
+      <c r="W19">
+        <v>0.002</v>
+      </c>
+      <c r="X19">
+        <v>0.084</v>
+      </c>
+      <c r="Y19">
+        <v>0.144</v>
+      </c>
+      <c r="Z19">
+        <v>0.154</v>
+      </c>
+      <c r="AA19">
+        <v>0.155</v>
+      </c>
+      <c r="AB19">
+        <v>0.142</v>
+      </c>
+      <c r="AC19">
+        <v>0.101</v>
+      </c>
+      <c r="AD19">
+        <v>0.076</v>
+      </c>
+      <c r="AE19">
+        <v>0.055</v>
+      </c>
+      <c r="AF19">
+        <v>0.038</v>
+      </c>
+      <c r="AG19">
+        <v>0.023</v>
+      </c>
+      <c r="AH19">
+        <v>0.011</v>
+      </c>
+      <c r="AI19">
+        <v>0.009</v>
+      </c>
+      <c r="AJ19">
+        <v>0.003</v>
+      </c>
+      <c r="AK19">
+        <v>0.002</v>
+      </c>
+      <c r="AL19">
+        <v>0.001</v>
+      </c>
+      <c r="AM19">
+        <v>0.002</v>
+      </c>
+      <c r="AN19">
+        <v>0.431</v>
+      </c>
+      <c r="AO19">
+        <v>0.345</v>
+      </c>
+      <c r="AP19">
+        <v>0.435</v>
+      </c>
+      <c r="AQ19">
+        <v>0.371</v>
+      </c>
+      <c r="AR19">
+        <v>0.409</v>
+      </c>
+      <c r="AS19">
+        <v>0.411</v>
+      </c>
+      <c r="AT19">
+        <v>0.431</v>
+      </c>
+      <c r="AU19">
+        <v>0.387</v>
+      </c>
+      <c r="AV19">
+        <v>0.231</v>
+      </c>
+      <c r="AW19">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49">
+      <c r="A20">
+        <v>824039</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20">
+        <v>5.069</v>
+      </c>
+      <c r="G20">
+        <v>0.61</v>
+      </c>
+      <c r="H20">
+        <v>0.105</v>
+      </c>
+      <c r="I20">
+        <v>0.331</v>
+      </c>
+      <c r="J20">
+        <v>0.081</v>
+      </c>
+      <c r="K20">
+        <v>0.203</v>
+      </c>
+      <c r="L20">
+        <v>1.192</v>
+      </c>
+      <c r="M20">
+        <v>0.094</v>
+      </c>
+      <c r="N20">
+        <v>1.642</v>
+      </c>
+      <c r="O20">
+        <v>5.892</v>
+      </c>
+      <c r="P20">
+        <v>3.517</v>
+      </c>
+      <c r="Q20">
+        <v>8.475</v>
+      </c>
+      <c r="R20">
+        <v>0.315</v>
+      </c>
+      <c r="S20">
+        <v>0.348</v>
+      </c>
+      <c r="T20">
+        <v>0.216</v>
+      </c>
+      <c r="U20">
+        <v>0.085</v>
+      </c>
+      <c r="V20">
+        <v>0.026</v>
+      </c>
+      <c r="W20">
+        <v>0.009</v>
+      </c>
+      <c r="X20">
+        <v>0.044</v>
+      </c>
+      <c r="Y20">
+        <v>0.073</v>
+      </c>
+      <c r="Z20">
+        <v>0.096</v>
+      </c>
+      <c r="AA20">
+        <v>0.134</v>
+      </c>
+      <c r="AB20">
+        <v>0.128</v>
+      </c>
+      <c r="AC20">
+        <v>0.131</v>
+      </c>
+      <c r="AD20">
+        <v>0.102</v>
+      </c>
+      <c r="AE20">
+        <v>0.088</v>
+      </c>
+      <c r="AF20">
+        <v>0.073</v>
+      </c>
+      <c r="AG20">
+        <v>0.042</v>
+      </c>
+      <c r="AH20">
+        <v>0.032</v>
+      </c>
+      <c r="AI20">
+        <v>0.02</v>
+      </c>
+      <c r="AJ20">
+        <v>0.015</v>
+      </c>
+      <c r="AK20">
+        <v>0.008</v>
+      </c>
+      <c r="AL20">
+        <v>0.007</v>
+      </c>
+      <c r="AM20">
+        <v>0.007</v>
+      </c>
+      <c r="AN20">
+        <v>0.637</v>
+      </c>
+      <c r="AO20">
+        <v>0.535</v>
+      </c>
+      <c r="AP20">
+        <v>0.548</v>
+      </c>
+      <c r="AQ20">
+        <v>0.57</v>
+      </c>
+      <c r="AR20">
+        <v>0.553</v>
+      </c>
+      <c r="AS20">
+        <v>0.557</v>
+      </c>
+      <c r="AT20">
+        <v>0.588</v>
+      </c>
+      <c r="AU20">
+        <v>0.593</v>
+      </c>
+      <c r="AV20">
+        <v>0.256</v>
+      </c>
+      <c r="AW20">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49">
+      <c r="A21">
+        <v>824120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21">
+        <v>5.423</v>
+      </c>
+      <c r="G21">
+        <v>0.546</v>
+      </c>
+      <c r="H21">
+        <v>0.106</v>
+      </c>
+      <c r="I21">
+        <v>0.282</v>
+      </c>
+      <c r="J21">
+        <v>0.084</v>
+      </c>
+      <c r="K21">
+        <v>0.259</v>
+      </c>
+      <c r="L21">
+        <v>1.411</v>
+      </c>
+      <c r="M21">
+        <v>0.197</v>
+      </c>
+      <c r="N21">
+        <v>1.864</v>
+      </c>
+      <c r="O21">
+        <v>5.587</v>
+      </c>
+      <c r="P21">
+        <v>3.213</v>
+      </c>
+      <c r="Q21">
+        <v>6.923</v>
+      </c>
+      <c r="R21">
+        <v>0.239</v>
+      </c>
+      <c r="S21">
+        <v>0.342</v>
+      </c>
+      <c r="T21">
+        <v>0.259</v>
+      </c>
+      <c r="U21">
+        <v>0.108</v>
+      </c>
+      <c r="V21">
+        <v>0.039</v>
+      </c>
+      <c r="W21">
+        <v>0.013</v>
+      </c>
+      <c r="X21">
+        <v>0.032</v>
+      </c>
+      <c r="Y21">
+        <v>0.056</v>
+      </c>
+      <c r="Z21">
+        <v>0.09</v>
+      </c>
+      <c r="AA21">
+        <v>0.124</v>
+      </c>
+      <c r="AB21">
+        <v>0.122</v>
+      </c>
+      <c r="AC21">
+        <v>0.128</v>
+      </c>
+      <c r="AD21">
+        <v>0.109</v>
+      </c>
+      <c r="AE21">
+        <v>0.1</v>
+      </c>
+      <c r="AF21">
+        <v>0.08</v>
+      </c>
+      <c r="AG21">
+        <v>0.053</v>
+      </c>
+      <c r="AH21">
+        <v>0.039</v>
+      </c>
+      <c r="AI21">
+        <v>0.024</v>
+      </c>
+      <c r="AJ21">
+        <v>0.02</v>
+      </c>
+      <c r="AK21">
+        <v>0.01</v>
+      </c>
+      <c r="AL21">
+        <v>0.003</v>
+      </c>
+      <c r="AM21">
+        <v>0.009</v>
+      </c>
+      <c r="AN21">
+        <v>0.681</v>
+      </c>
+      <c r="AO21">
+        <v>0.617</v>
+      </c>
+      <c r="AP21">
+        <v>0.649</v>
+      </c>
+      <c r="AQ21">
+        <v>0.606</v>
+      </c>
+      <c r="AR21">
+        <v>0.606</v>
+      </c>
+      <c r="AS21">
+        <v>0.608</v>
+      </c>
+      <c r="AT21">
+        <v>0.579</v>
+      </c>
+      <c r="AU21">
+        <v>0.554</v>
+      </c>
+      <c r="AV21">
+        <v>0.28</v>
+      </c>
+      <c r="AW21">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49">
+      <c r="A22">
+        <v>824201</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22">
+        <v>4.036</v>
+      </c>
+      <c r="G22">
+        <v>0.414</v>
+      </c>
+      <c r="H22">
+        <v>0.086</v>
+      </c>
+      <c r="I22">
+        <v>0.174</v>
+      </c>
+      <c r="J22">
+        <v>0.103</v>
+      </c>
+      <c r="K22">
+        <v>0.36</v>
+      </c>
+      <c r="L22">
+        <v>1.114</v>
+      </c>
+      <c r="M22">
+        <v>0.064</v>
+      </c>
+      <c r="N22">
+        <v>1.469</v>
+      </c>
+      <c r="O22">
+        <v>4.917</v>
+      </c>
+      <c r="P22">
+        <v>3.093</v>
+      </c>
+      <c r="Q22">
+        <v>8.258</v>
+      </c>
+      <c r="R22">
+        <v>0.338</v>
+      </c>
+      <c r="S22">
+        <v>0.354</v>
+      </c>
+      <c r="T22">
+        <v>0.198</v>
+      </c>
+      <c r="U22">
+        <v>0.082</v>
+      </c>
+      <c r="V22">
+        <v>0.021</v>
+      </c>
+      <c r="W22">
+        <v>0.006</v>
+      </c>
+      <c r="X22">
+        <v>0.077</v>
+      </c>
+      <c r="Y22">
+        <v>0.114</v>
+      </c>
+      <c r="Z22">
+        <v>0.144</v>
+      </c>
+      <c r="AA22">
+        <v>0.144</v>
+      </c>
+      <c r="AB22">
+        <v>0.138</v>
+      </c>
+      <c r="AC22">
+        <v>0.111</v>
+      </c>
+      <c r="AD22">
+        <v>0.097</v>
+      </c>
+      <c r="AE22">
+        <v>0.065</v>
+      </c>
+      <c r="AF22">
+        <v>0.038</v>
+      </c>
+      <c r="AG22">
+        <v>0.025</v>
+      </c>
+      <c r="AH22">
+        <v>0.023</v>
+      </c>
+      <c r="AI22">
+        <v>0.009</v>
+      </c>
+      <c r="AJ22">
+        <v>0.007</v>
+      </c>
+      <c r="AK22">
+        <v>0.003</v>
+      </c>
+      <c r="AL22">
+        <v>0.003</v>
+      </c>
+      <c r="AM22">
+        <v>0.002</v>
+      </c>
+      <c r="AN22">
+        <v>0.467</v>
+      </c>
+      <c r="AO22">
+        <v>0.369</v>
+      </c>
+      <c r="AP22">
+        <v>0.437</v>
+      </c>
+      <c r="AQ22">
+        <v>0.405</v>
+      </c>
+      <c r="AR22">
+        <v>0.418</v>
+      </c>
+      <c r="AS22">
+        <v>0.439</v>
+      </c>
+      <c r="AT22">
+        <v>0.493</v>
+      </c>
+      <c r="AU22">
+        <v>0.52</v>
+      </c>
+      <c r="AV22">
+        <v>0.292</v>
+      </c>
+      <c r="AW22">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49">
+      <c r="A23">
+        <v>824283</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23">
+        <v>5.456</v>
+      </c>
+      <c r="G23">
+        <v>0.635</v>
+      </c>
+      <c r="H23">
+        <v>0.107</v>
+      </c>
+      <c r="I23">
+        <v>0.358</v>
+      </c>
+      <c r="J23">
+        <v>0.084</v>
+      </c>
+      <c r="K23">
+        <v>0.178</v>
+      </c>
+      <c r="L23">
+        <v>1.013</v>
+      </c>
+      <c r="M23">
+        <v>0.127</v>
+      </c>
+      <c r="N23">
+        <v>1.75</v>
+      </c>
+      <c r="O23">
+        <v>5.794</v>
+      </c>
+      <c r="P23">
+        <v>5.03</v>
+      </c>
+      <c r="Q23">
+        <v>8.63</v>
+      </c>
+      <c r="R23">
+        <v>0.352</v>
+      </c>
+      <c r="S23">
+        <v>0.387</v>
+      </c>
+      <c r="T23">
+        <v>0.178</v>
+      </c>
+      <c r="U23">
+        <v>0.066</v>
+      </c>
+      <c r="V23">
+        <v>0.013</v>
+      </c>
+      <c r="W23">
+        <v>0.004</v>
+      </c>
+      <c r="X23">
+        <v>0.031</v>
+      </c>
+      <c r="Y23">
+        <v>0.064</v>
+      </c>
+      <c r="Z23">
+        <v>0.103</v>
+      </c>
+      <c r="AA23">
+        <v>0.118</v>
+      </c>
+      <c r="AB23">
+        <v>0.121</v>
+      </c>
+      <c r="AC23">
+        <v>0.125</v>
+      </c>
+      <c r="AD23">
+        <v>0.112</v>
+      </c>
+      <c r="AE23">
+        <v>0.084</v>
+      </c>
+      <c r="AF23">
+        <v>0.069</v>
+      </c>
+      <c r="AG23">
+        <v>0.049</v>
+      </c>
+      <c r="AH23">
+        <v>0.036</v>
+      </c>
+      <c r="AI23">
+        <v>0.03</v>
+      </c>
+      <c r="AJ23">
+        <v>0.024</v>
+      </c>
+      <c r="AK23">
+        <v>0.012</v>
+      </c>
+      <c r="AL23">
+        <v>0.008</v>
+      </c>
+      <c r="AM23">
+        <v>0.014</v>
+      </c>
+      <c r="AN23">
+        <v>0.674</v>
+      </c>
+      <c r="AO23">
+        <v>0.591</v>
+      </c>
+      <c r="AP23">
+        <v>0.615</v>
+      </c>
+      <c r="AQ23">
+        <v>0.569</v>
+      </c>
+      <c r="AR23">
+        <v>0.646</v>
+      </c>
+      <c r="AS23">
+        <v>0.631</v>
+      </c>
+      <c r="AT23">
+        <v>0.617</v>
+      </c>
+      <c r="AU23">
+        <v>0.637</v>
+      </c>
+      <c r="AV23">
+        <v>0.217</v>
+      </c>
+      <c r="AW23">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49">
+      <c r="A24">
+        <v>824363</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24">
+        <v>6.435</v>
+      </c>
+      <c r="G24">
+        <v>0.526</v>
+      </c>
+      <c r="H24">
+        <v>0.091</v>
+      </c>
+      <c r="I24">
+        <v>0.3</v>
+      </c>
+      <c r="J24">
+        <v>0.078</v>
+      </c>
+      <c r="K24">
+        <v>0.299</v>
+      </c>
+      <c r="L24">
+        <v>1.225</v>
+      </c>
+      <c r="M24">
+        <v>0.279</v>
+      </c>
+      <c r="N24">
+        <v>2.363</v>
+      </c>
+      <c r="O24">
+        <v>6.99</v>
+      </c>
+      <c r="P24">
+        <v>3.359</v>
+      </c>
+      <c r="Q24">
+        <v>7.986</v>
+      </c>
+      <c r="R24">
+        <v>0.303</v>
+      </c>
+      <c r="S24">
+        <v>0.348</v>
+      </c>
+      <c r="T24">
+        <v>0.22</v>
+      </c>
+      <c r="U24">
+        <v>0.095</v>
+      </c>
+      <c r="V24">
+        <v>0.025</v>
+      </c>
+      <c r="W24">
+        <v>0.01</v>
+      </c>
+      <c r="X24">
+        <v>0.018</v>
+      </c>
+      <c r="Y24">
+        <v>0.043</v>
+      </c>
+      <c r="Z24">
+        <v>0.061</v>
+      </c>
+      <c r="AA24">
+        <v>0.095</v>
+      </c>
+      <c r="AB24">
+        <v>0.102</v>
+      </c>
+      <c r="AC24">
+        <v>0.11</v>
+      </c>
+      <c r="AD24">
+        <v>0.116</v>
+      </c>
+      <c r="AE24">
+        <v>0.104</v>
+      </c>
+      <c r="AF24">
+        <v>0.09</v>
+      </c>
+      <c r="AG24">
+        <v>0.077</v>
+      </c>
+      <c r="AH24">
+        <v>0.063</v>
+      </c>
+      <c r="AI24">
+        <v>0.038</v>
+      </c>
+      <c r="AJ24">
+        <v>0.026</v>
+      </c>
+      <c r="AK24">
+        <v>0.019</v>
+      </c>
+      <c r="AL24">
+        <v>0.013</v>
+      </c>
+      <c r="AM24">
+        <v>0.023</v>
+      </c>
+      <c r="AN24">
+        <v>0.636</v>
+      </c>
+      <c r="AO24">
+        <v>0.708</v>
+      </c>
+      <c r="AP24">
+        <v>0.792</v>
+      </c>
+      <c r="AQ24">
+        <v>0.801</v>
+      </c>
+      <c r="AR24">
+        <v>0.803</v>
+      </c>
+      <c r="AS24">
+        <v>0.754</v>
+      </c>
+      <c r="AT24">
+        <v>0.675</v>
+      </c>
+      <c r="AU24">
+        <v>0.669</v>
+      </c>
+      <c r="AV24">
+        <v>0.31</v>
+      </c>
+      <c r="AW24">
+        <v>0.101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49">
+      <c r="A25">
+        <v>824684</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25">
+        <v>7.472</v>
+      </c>
+      <c r="G25">
+        <v>0.644</v>
+      </c>
+      <c r="H25">
+        <v>0.091</v>
+      </c>
+      <c r="I25">
+        <v>0.41</v>
+      </c>
+      <c r="J25">
+        <v>0.065</v>
+      </c>
+      <c r="K25">
+        <v>0.205</v>
+      </c>
+      <c r="L25">
+        <v>1.985</v>
+      </c>
+      <c r="M25">
+        <v>0.146</v>
+      </c>
+      <c r="N25">
+        <v>1.811</v>
+      </c>
+      <c r="O25">
+        <v>6.038</v>
+      </c>
+      <c r="P25">
+        <v>5.998</v>
+      </c>
+      <c r="Q25">
+        <v>8.186</v>
+      </c>
+      <c r="R25">
+        <v>0.14</v>
+      </c>
+      <c r="S25">
+        <v>0.27</v>
+      </c>
+      <c r="T25">
+        <v>0.269</v>
+      </c>
+      <c r="U25">
+        <v>0.177</v>
+      </c>
+      <c r="V25">
+        <v>0.092</v>
+      </c>
+      <c r="W25">
+        <v>0.052</v>
+      </c>
+      <c r="X25">
+        <v>0.011</v>
+      </c>
+      <c r="Y25">
+        <v>0.025</v>
+      </c>
+      <c r="Z25">
+        <v>0.047</v>
+      </c>
+      <c r="AA25">
+        <v>0.064</v>
+      </c>
+      <c r="AB25">
+        <v>0.086</v>
+      </c>
+      <c r="AC25">
+        <v>0.094</v>
+      </c>
+      <c r="AD25">
+        <v>0.104</v>
+      </c>
+      <c r="AE25">
+        <v>0.112</v>
+      </c>
+      <c r="AF25">
+        <v>0.096</v>
+      </c>
+      <c r="AG25">
+        <v>0.088</v>
+      </c>
+      <c r="AH25">
+        <v>0.072</v>
+      </c>
+      <c r="AI25">
+        <v>0.055</v>
+      </c>
+      <c r="AJ25">
+        <v>0.044</v>
+      </c>
+      <c r="AK25">
+        <v>0.032</v>
+      </c>
+      <c r="AL25">
+        <v>0.024</v>
+      </c>
+      <c r="AM25">
+        <v>0.045</v>
+      </c>
+      <c r="AN25">
+        <v>0.985</v>
+      </c>
+      <c r="AO25">
+        <v>0.876</v>
+      </c>
+      <c r="AP25">
+        <v>0.887</v>
+      </c>
+      <c r="AQ25">
+        <v>0.91</v>
+      </c>
+      <c r="AR25">
+        <v>0.854</v>
+      </c>
+      <c r="AS25">
+        <v>0.793</v>
+      </c>
+      <c r="AT25">
+        <v>0.795</v>
+      </c>
+      <c r="AU25">
+        <v>0.816</v>
+      </c>
+      <c r="AV25">
+        <v>0.289</v>
+      </c>
+      <c r="AW25">
+        <v>0.106</v>
       </c>
     </row>
   </sheetData>
